--- a/table/Datas/#PanchigiSetup.xlsx
+++ b/table/Datas/#PanchigiSetup.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,11 +429,6 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>coin_count</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
           <t>formation</t>
         </is>
       </c>
@@ -451,11 +446,6 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
           <t>string</t>
         </is>
       </c>
@@ -479,11 +469,6 @@
         </is>
       </c>
       <c r="C4" t="inlineStr">
-        <is>
-          <t>coin_count</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
         <is>
           <t>formation</t>
         </is>
@@ -493,10 +478,7 @@
       <c r="B5" t="n">
         <v>2</v>
       </c>
-      <c r="C5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>FourInLine</t>
         </is>
@@ -506,10 +488,7 @@
       <c r="B6" t="n">
         <v>3</v>
       </c>
-      <c r="C6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>SixInLine</t>
         </is>
@@ -519,12 +498,9 @@
       <c r="B7" t="n">
         <v>4</v>
       </c>
-      <c r="C7" t="n">
-        <v>8</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>FourByTwo</t>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EightInLine</t>
         </is>
       </c>
     </row>

--- a/table/Datas/#PanchigiSetup.xlsx
+++ b/table/Datas/#PanchigiSetup.xlsx
@@ -500,7 +500,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>EightInLine</t>
+          <t>FourByTwo</t>
         </is>
       </c>
     </row>

--- a/table/Datas/#PanchigiSetup.xlsx
+++ b/table/Datas/#PanchigiSetup.xlsx
@@ -480,7 +480,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FourInLine</t>
+          <t>SixInLine</t>
         </is>
       </c>
     </row>
